--- a/data/trans_orig/P19C02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116761</t>
+          <t>117099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154445</t>
+          <t>154558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98265</t>
+          <t>96872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128366</t>
+          <t>128556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224494</t>
+          <t>225185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275039</t>
+          <t>275980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231857</t>
+          <t>231744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269541</t>
+          <t>269203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139921</t>
+          <t>139731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170022</t>
+          <t>171415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>379551</t>
+          <t>378610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>430096</t>
+          <t>429405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100461</t>
+          <t>98962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133391</t>
+          <t>133005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115665</t>
+          <t>113398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149662</t>
+          <t>149017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224147</t>
+          <t>223330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271807</t>
+          <t>273635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>166814</t>
+          <t>167200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199744</t>
+          <t>201243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183903</t>
+          <t>184548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217900</t>
+          <t>220167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361963</t>
+          <t>360135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409623</t>
+          <t>410440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111991</t>
+          <t>112571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151234</t>
+          <t>151053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38192</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159758</t>
+          <t>158801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204419</t>
+          <t>201228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279033</t>
+          <t>279214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318276</t>
+          <t>317696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>79858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101876</t>
+          <t>101239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>365916</t>
+          <t>369107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410577</t>
+          <t>411534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182942</t>
+          <t>183081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234626</t>
+          <t>236946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149645</t>
+          <t>152184</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194577</t>
+          <t>194246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348159</t>
+          <t>348717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414957</t>
+          <t>416041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>636828</t>
+          <t>634508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>688512</t>
+          <t>688373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>399760</t>
+          <t>400091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>444692</t>
+          <t>442153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1050834</t>
+          <t>1049750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1117632</t>
+          <t>1117074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57308</t>
+          <t>56381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91196</t>
+          <t>91727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129091</t>
+          <t>129035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130544</t>
+          <t>133218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178046</t>
+          <t>174604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190619</t>
+          <t>191546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215243</t>
+          <t>214637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326989</t>
+          <t>327045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>364884</t>
+          <t>364353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>525961</t>
+          <t>529403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>573463</t>
+          <t>570789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>52970</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78291</t>
+          <t>79791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>198205</t>
+          <t>199878</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247896</t>
+          <t>250337</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>260778</t>
+          <t>261181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>321013</t>
+          <t>320234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133942</t>
+          <t>132442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159144</t>
+          <t>159263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>696703</t>
+          <t>694262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>746394</t>
+          <t>744721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>835819</t>
+          <t>836598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>896054</t>
+          <t>895651</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>654871</t>
+          <t>660576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>745949</t>
+          <t>751767</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>756653</t>
+          <t>755241</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>843521</t>
+          <t>847017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1434256</t>
+          <t>1438277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1564606</t>
+          <t>1570752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1702439</t>
+          <t>1696621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1793517</t>
+          <t>1787812</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1893415</t>
+          <t>1889919</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1980283</t>
+          <t>1981695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3620718</t>
+          <t>3614572</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3751068</t>
+          <t>3747047</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142959</t>
+          <t>142863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184769</t>
+          <t>185362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100431</t>
+          <t>102577</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136554</t>
+          <t>136578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251257</t>
+          <t>255695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309786</t>
+          <t>310025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209527</t>
+          <t>208934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251337</t>
+          <t>251433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157400</t>
+          <t>157376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>193523</t>
+          <t>191377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378465</t>
+          <t>378226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436994</t>
+          <t>432556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136723</t>
+          <t>138339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178883</t>
+          <t>180102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108705</t>
+          <t>110220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147413</t>
+          <t>144701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255199</t>
+          <t>257837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310978</t>
+          <t>311794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>204841</t>
+          <t>203622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247001</t>
+          <t>245385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>166088</t>
+          <t>168800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204796</t>
+          <t>203281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386247</t>
+          <t>385431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442026</t>
+          <t>439388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144147</t>
+          <t>145710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186125</t>
+          <t>187952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>62454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92103</t>
+          <t>93397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217206</t>
+          <t>215581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267454</t>
+          <t>268739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>349363</t>
+          <t>347536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>391341</t>
+          <t>389778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149604</t>
+          <t>148310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178112</t>
+          <t>179253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509741</t>
+          <t>508456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559989</t>
+          <t>561614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209078</t>
+          <t>211378</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265940</t>
+          <t>266861</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223753</t>
+          <t>223688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>274234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>450201</t>
+          <t>451401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>525120</t>
+          <t>528535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>704784</t>
+          <t>703863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>761646</t>
+          <t>759346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422919</t>
+          <t>424693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475174</t>
+          <t>475239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1144531</t>
+          <t>1141116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1219450</t>
+          <t>1218250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65530</t>
+          <t>64073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>95597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153053</t>
+          <t>153314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200702</t>
+          <t>199290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227879</t>
+          <t>227938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282357</t>
+          <t>283486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>306282</t>
+          <t>307715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337782</t>
+          <t>339239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>470060</t>
+          <t>471472</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>517709</t>
+          <t>517448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>791717</t>
+          <t>790588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>846195</t>
+          <t>846136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47541</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73510</t>
+          <t>73666</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>210011</t>
+          <t>207335</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>264953</t>
+          <t>264609</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>263561</t>
+          <t>264644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>326121</t>
+          <t>325237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147693</t>
+          <t>147537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173662</t>
+          <t>173065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>660432</t>
+          <t>660776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>715374</t>
+          <t>718050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>820467</t>
+          <t>821351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883027</t>
+          <t>881944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>810786</t>
+          <t>812384</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>914431</t>
+          <t>910713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>928105</t>
+          <t>929685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1030444</t>
+          <t>1037927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1769258</t>
+          <t>1772970</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1921187</t>
+          <t>1918818</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1994317</t>
+          <t>1998035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2097962</t>
+          <t>2096364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2113793</t>
+          <t>2106310</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2216132</t>
+          <t>2214552</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4131798</t>
+          <t>4134167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4283727</t>
+          <t>4280015</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174706</t>
+          <t>173919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>215235</t>
+          <t>213185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121295</t>
+          <t>121710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157140</t>
+          <t>157925</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>304904</t>
+          <t>306604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>359616</t>
+          <t>359495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172379</t>
+          <t>174429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>212908</t>
+          <t>213695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158676</t>
+          <t>157891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194521</t>
+          <t>194106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343814</t>
+          <t>343935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>398526</t>
+          <t>396826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110106</t>
+          <t>110267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148068</t>
+          <t>147201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137459</t>
+          <t>139266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175915</t>
+          <t>176059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260910</t>
+          <t>260570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>314472</t>
+          <t>312305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168590</t>
+          <t>169457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206552</t>
+          <t>206391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>157660</t>
+          <t>157516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196116</t>
+          <t>194309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335760</t>
+          <t>337927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389322</t>
+          <t>389662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109048</t>
+          <t>109213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147934</t>
+          <t>147683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41300</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63788</t>
+          <t>64324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157954</t>
+          <t>159072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202815</t>
+          <t>203630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257277</t>
+          <t>257528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296163</t>
+          <t>295998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75633</t>
+          <t>75097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98121</t>
+          <t>98666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341818</t>
+          <t>341003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>386679</t>
+          <t>385561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236605</t>
+          <t>238874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289993</t>
+          <t>294707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238387</t>
+          <t>237558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291005</t>
+          <t>289726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>493081</t>
+          <t>489399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>569552</t>
+          <t>567901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589512</t>
+          <t>584798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642900</t>
+          <t>640631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393026</t>
+          <t>394305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>445644</t>
+          <t>446473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>993984</t>
+          <t>995635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1070455</t>
+          <t>1074137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115184</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155597</t>
+          <t>156089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162779</t>
+          <t>162287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208569</t>
+          <t>206906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>289033</t>
+          <t>292065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>347256</t>
+          <t>351414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269572</t>
+          <t>269080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>309985</t>
+          <t>308285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>348912</t>
+          <t>350575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394702</t>
+          <t>395194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>635394</t>
+          <t>631236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>693617</t>
+          <t>690585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,28%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60999</t>
+          <t>60026</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88270</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>235516</t>
+          <t>235923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>287913</t>
+          <t>291078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>312033</t>
+          <t>309549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>370303</t>
+          <t>372037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153278</t>
+          <t>152318</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180549</t>
+          <t>181522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>537376</t>
+          <t>534211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>589773</t>
+          <t>589366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>696534</t>
+          <t>694800</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>754804</t>
+          <t>757288</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>875585</t>
+          <t>877033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>971381</t>
+          <t>980614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1008435</t>
+          <t>1011514</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1109481</t>
+          <t>1120205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1923295</t>
+          <t>1918022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2061676</t>
+          <t>2058594</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,35%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1684324</t>
+          <t>1675091</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1780120</t>
+          <t>1778672</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1746132</t>
+          <t>1735408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1847178</t>
+          <t>1844099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3449642</t>
+          <t>3452724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3588023</t>
+          <t>3593296</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>252100</t>
+          <t>253868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299250</t>
+          <t>300948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226369</t>
+          <t>226837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>262233</t>
+          <t>263884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>493102</t>
+          <t>491747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>550899</t>
+          <t>551741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199936</t>
+          <t>198238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247086</t>
+          <t>245318</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178692</t>
+          <t>177041</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214556</t>
+          <t>214088</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>389212</t>
+          <t>388370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>447009</t>
+          <t>448364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>225801</t>
+          <t>227846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269342</t>
+          <t>272082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206919</t>
+          <t>206826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239096</t>
+          <t>239625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>444409</t>
+          <t>441608</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>500455</t>
+          <t>499424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179076</t>
+          <t>176336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222617</t>
+          <t>220572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138510</t>
+          <t>137981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>170687</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>325568</t>
+          <t>326599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381614</t>
+          <t>384415</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71336</t>
+          <t>73971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>326668</t>
+          <t>326688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82766</t>
+          <t>83285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102755</t>
+          <t>103893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129224</t>
+          <t>122576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>428259</t>
+          <t>425761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334061</t>
+          <t>334041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>589393</t>
+          <t>586758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62213</t>
+          <t>61075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82202</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>397438</t>
+          <t>399936</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>696473</t>
+          <t>703121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>379144</t>
+          <t>376075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>443245</t>
+          <t>444526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>456008</t>
+          <t>453225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>747930</t>
+          <t>748382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>844358</t>
+          <t>847170</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1224860</t>
+          <t>1315745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>553941</t>
+          <t>552660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>618042</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210939</t>
+          <t>210487</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502861</t>
+          <t>505644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731195</t>
+          <t>640310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1111697</t>
+          <t>1108885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144566</t>
+          <t>147890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189708</t>
+          <t>190658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>212507</t>
+          <t>221257</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>339758</t>
+          <t>338205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371586</t>
+          <t>381774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>509041</t>
+          <t>511541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249144</t>
+          <t>248194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294286</t>
+          <t>290962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474223</t>
+          <t>475776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>601474</t>
+          <t>592724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743792</t>
+          <t>741292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>881247</t>
+          <t>871059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102369</t>
+          <t>100146</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152480</t>
+          <t>153062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>291168</t>
+          <t>292492</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343862</t>
+          <t>343560</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>408952</t>
+          <t>410970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>482149</t>
+          <t>483461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80732</t>
+          <t>80150</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130843</t>
+          <t>133066</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>400048</t>
+          <t>400350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>452742</t>
+          <t>451418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>494973</t>
+          <t>493661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>568170</t>
+          <t>566152</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1063843</t>
+          <t>1067908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1561041</t>
+          <t>1563159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1609057</t>
+          <t>1602819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2116298</t>
+          <t>2114193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2889766</t>
+          <t>2822385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3473206</t>
+          <t>3496077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1716541</t>
+          <t>1714423</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2213739</t>
+          <t>2209674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1383961</t>
+          <t>1386066</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1891202</t>
+          <t>1897440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3304635</t>
+          <t>3281764</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3888075</t>
+          <t>3955456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117099</t>
+          <t>116992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154558</t>
+          <t>154658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96872</t>
+          <t>97276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128556</t>
+          <t>128562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225185</t>
+          <t>226117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275980</t>
+          <t>277377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231744</t>
+          <t>231644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269203</t>
+          <t>269310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139731</t>
+          <t>139725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171415</t>
+          <t>171011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378610</t>
+          <t>377213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>429405</t>
+          <t>428473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98962</t>
+          <t>100512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133005</t>
+          <t>135535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113398</t>
+          <t>114753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149017</t>
+          <t>151162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223330</t>
+          <t>221437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273635</t>
+          <t>273896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167200</t>
+          <t>164670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201243</t>
+          <t>199693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184548</t>
+          <t>182403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220167</t>
+          <t>218812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>360135</t>
+          <t>359874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410440</t>
+          <t>412333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112571</t>
+          <t>114103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151053</t>
+          <t>151465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60210</t>
+          <t>60752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158801</t>
+          <t>158407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201228</t>
+          <t>202940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279214</t>
+          <t>278802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317696</t>
+          <t>316164</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79858</t>
+          <t>79316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>369107</t>
+          <t>367395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>411534</t>
+          <t>411928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183081</t>
+          <t>183587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>236946</t>
+          <t>233878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152184</t>
+          <t>148556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194246</t>
+          <t>194677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348717</t>
+          <t>344860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>416041</t>
+          <t>413830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634508</t>
+          <t>637576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>688373</t>
+          <t>687867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>400091</t>
+          <t>399660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>442153</t>
+          <t>445781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1049750</t>
+          <t>1051961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1117074</t>
+          <t>1120931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56381</t>
+          <t>57231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91727</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129035</t>
+          <t>126946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133218</t>
+          <t>128607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174604</t>
+          <t>176223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191546</t>
+          <t>190696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214637</t>
+          <t>215611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327045</t>
+          <t>329134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>364353</t>
+          <t>366850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>529403</t>
+          <t>527784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570789</t>
+          <t>575400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>53199</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79791</t>
+          <t>78649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>199878</t>
+          <t>199759</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>250337</t>
+          <t>250178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261181</t>
+          <t>261717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320234</t>
+          <t>319262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132442</t>
+          <t>133584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159263</t>
+          <t>159034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>694262</t>
+          <t>694421</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>744721</t>
+          <t>744840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>836598</t>
+          <t>837570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>895651</t>
+          <t>895115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>660576</t>
+          <t>654573</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>751767</t>
+          <t>746775</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>755241</t>
+          <t>750332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>847017</t>
+          <t>842986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1438277</t>
+          <t>1432226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1562259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1696621</t>
+          <t>1701613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1787812</t>
+          <t>1793815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1889919</t>
+          <t>1893950</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1981695</t>
+          <t>1986604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3614572</t>
+          <t>3623065</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3747047</t>
+          <t>3753098</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142863</t>
+          <t>140677</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185362</t>
+          <t>183075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102577</t>
+          <t>100629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>135717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>255695</t>
+          <t>256515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>310025</t>
+          <t>311911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208934</t>
+          <t>211221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251433</t>
+          <t>253619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157376</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191377</t>
+          <t>193325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378226</t>
+          <t>376340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>432556</t>
+          <t>431736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138339</t>
+          <t>136066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180102</t>
+          <t>178064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110220</t>
+          <t>108449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144701</t>
+          <t>146303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257837</t>
+          <t>254961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>311794</t>
+          <t>309667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203622</t>
+          <t>205660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245385</t>
+          <t>247658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168800</t>
+          <t>167198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203281</t>
+          <t>205052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385431</t>
+          <t>387558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439388</t>
+          <t>442264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145710</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187952</t>
+          <t>186725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62454</t>
+          <t>63453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93397</t>
+          <t>92604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215581</t>
+          <t>215393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268739</t>
+          <t>269188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>347536</t>
+          <t>348763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389778</t>
+          <t>392264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148310</t>
+          <t>149103</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179253</t>
+          <t>178254</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>508456</t>
+          <t>508007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561614</t>
+          <t>561802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211378</t>
+          <t>210886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266861</t>
+          <t>264120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223688</t>
+          <t>224555</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274234</t>
+          <t>276804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>451401</t>
+          <t>445747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528535</t>
+          <t>524721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>703863</t>
+          <t>706604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>759346</t>
+          <t>759838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424693</t>
+          <t>422123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475239</t>
+          <t>474372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1141116</t>
+          <t>1144930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218250</t>
+          <t>1223904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>64193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>94288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153314</t>
+          <t>152860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199290</t>
+          <t>200597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227938</t>
+          <t>227559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283486</t>
+          <t>281955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307715</t>
+          <t>309024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339239</t>
+          <t>339119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471472</t>
+          <t>470165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>517448</t>
+          <t>517902</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>790588</t>
+          <t>792119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>846136</t>
+          <t>846515</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48138</t>
+          <t>47862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73666</t>
+          <t>73727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>207335</t>
+          <t>208954</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>264609</t>
+          <t>262179</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>264644</t>
+          <t>265719</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>325237</t>
+          <t>325521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147537</t>
+          <t>147476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173065</t>
+          <t>173341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>660776</t>
+          <t>663206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>718050</t>
+          <t>716431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>821351</t>
+          <t>821067</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>881944</t>
+          <t>880869</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>812384</t>
+          <t>808228</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>910713</t>
+          <t>910707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>929685</t>
+          <t>926307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1037927</t>
+          <t>1034199</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1772970</t>
+          <t>1767352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1918818</t>
+          <t>1920054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1998035</t>
+          <t>1998041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2096364</t>
+          <t>2100520</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2106310</t>
+          <t>2110038</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2214552</t>
+          <t>2217930</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4134167</t>
+          <t>4132931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4280015</t>
+          <t>4285633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173919</t>
+          <t>171035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>213185</t>
+          <t>213785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121710</t>
+          <t>122703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157925</t>
+          <t>158804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306604</t>
+          <t>308553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>359495</t>
+          <t>363510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174429</t>
+          <t>173829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213695</t>
+          <t>216579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157891</t>
+          <t>157012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194106</t>
+          <t>193113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343935</t>
+          <t>339920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>396826</t>
+          <t>394877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110267</t>
+          <t>110368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147201</t>
+          <t>146179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139266</t>
+          <t>138149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176059</t>
+          <t>175759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260570</t>
+          <t>260507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312305</t>
+          <t>311413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169457</t>
+          <t>170479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206391</t>
+          <t>206290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>157516</t>
+          <t>157816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194309</t>
+          <t>195426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337927</t>
+          <t>338819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389662</t>
+          <t>389725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109213</t>
+          <t>110502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147683</t>
+          <t>146585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64324</t>
+          <t>64101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159072</t>
+          <t>158668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203630</t>
+          <t>203349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257528</t>
+          <t>258626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295998</t>
+          <t>294709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75097</t>
+          <t>75320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98666</t>
+          <t>98424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341003</t>
+          <t>341284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>385561</t>
+          <t>385965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238874</t>
+          <t>237436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294707</t>
+          <t>290438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237558</t>
+          <t>239412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289726</t>
+          <t>290642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>489399</t>
+          <t>491300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>567901</t>
+          <t>565260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>584798</t>
+          <t>589067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640631</t>
+          <t>642069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>394305</t>
+          <t>393389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>446473</t>
+          <t>444619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>995635</t>
+          <t>998276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1074137</t>
+          <t>1072236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116884</t>
+          <t>115930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156089</t>
+          <t>154784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162287</t>
+          <t>162741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206906</t>
+          <t>207504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>292065</t>
+          <t>290613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>351414</t>
+          <t>352246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269080</t>
+          <t>270385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>308285</t>
+          <t>309239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350575</t>
+          <t>349977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>394740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>631236</t>
+          <t>630404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>690585</t>
+          <t>692037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60026</t>
+          <t>61205</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89230</t>
+          <t>92454</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>235923</t>
+          <t>236145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>291078</t>
+          <t>292171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>309549</t>
+          <t>305190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>372037</t>
+          <t>367183</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152318</t>
+          <t>149094</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181522</t>
+          <t>180343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>534211</t>
+          <t>533118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>589366</t>
+          <t>589144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>694800</t>
+          <t>699654</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>757288</t>
+          <t>761647</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>877033</t>
+          <t>873435</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>980614</t>
+          <t>975722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1011514</t>
+          <t>1010963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1120205</t>
+          <t>1115534</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1918022</t>
+          <t>1913794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2058594</t>
+          <t>2054987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1675091</t>
+          <t>1679983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1778672</t>
+          <t>1782270</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1735408</t>
+          <t>1740079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1844099</t>
+          <t>1844650</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3452724</t>
+          <t>3456331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3593296</t>
+          <t>3597524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>276367</t>
+          <t>306605</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>253868</t>
+          <t>280005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>300948</t>
+          <t>329607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>245602</t>
+          <t>268006</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226837</t>
+          <t>249231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>263884</t>
+          <t>285810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>521969</t>
+          <t>574611</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>491747</t>
+          <t>541998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>551741</t>
+          <t>603182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>222819</t>
+          <t>235610</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198238</t>
+          <t>212608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245318</t>
+          <t>262210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>195323</t>
+          <t>213321</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177041</t>
+          <t>195517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214088</t>
+          <t>232096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>418142</t>
+          <t>448930</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388370</t>
+          <t>420359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>448364</t>
+          <t>481543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>499186</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>499186</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>499186</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>940111</t>
+          <t>1023541</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>940111</t>
+          <t>1023541</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>940111</t>
+          <t>1023541</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>247718</t>
+          <t>267298</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>227846</t>
+          <t>245702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>272082</t>
+          <t>290053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>224004</t>
+          <t>244959</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206826</t>
+          <t>226668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239625</t>
+          <t>263137</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>471721</t>
+          <t>512258</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>441608</t>
+          <t>483668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>499424</t>
+          <t>539555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>200700</t>
+          <t>212034</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176336</t>
+          <t>189279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220572</t>
+          <t>233630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>153602</t>
+          <t>172961</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137981</t>
+          <t>154783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>170780</t>
+          <t>191252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>354302</t>
+          <t>384995</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>326599</t>
+          <t>357698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384415</t>
+          <t>413585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>199977</t>
+          <t>226186</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>205974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>326688</t>
+          <t>248782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>93425</t>
+          <t>104185</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83285</t>
+          <t>91906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103893</t>
+          <t>116019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>293402</t>
+          <t>330371</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122576</t>
+          <t>307748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>425761</t>
+          <t>356499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>460752</t>
+          <t>237679</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334041</t>
+          <t>215083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586758</t>
+          <t>257891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>80648</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61075</t>
+          <t>68814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>92927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>532295</t>
+          <t>318327</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>399936</t>
+          <t>292199</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703121</t>
+          <t>340950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>409467</t>
+          <t>448079</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>376075</t>
+          <t>410572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>444526</t>
+          <t>487234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>570342</t>
+          <t>407212</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>453225</t>
+          <t>381673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>748382</t>
+          <t>434363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>979809</t>
+          <t>855291</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>847170</t>
+          <t>815048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1315745</t>
+          <t>902457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>587719</t>
+          <t>646698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>552660</t>
+          <t>607543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>684205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>388527</t>
+          <t>429578</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210487</t>
+          <t>402427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505644</t>
+          <t>455117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>976246</t>
+          <t>1076276</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>640310</t>
+          <t>1029110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1108885</t>
+          <t>1116519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>997186</t>
+          <t>1094777</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>997186</t>
+          <t>1094777</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>997186</t>
+          <t>1094777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1956055</t>
+          <t>1931567</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1956055</t>
+          <t>1931567</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1956055</t>
+          <t>1931567</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>167231</t>
+          <t>189880</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147890</t>
+          <t>168414</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190658</t>
+          <t>216934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>294894</t>
+          <t>340155</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221257</t>
+          <t>316635</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338205</t>
+          <t>364362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>462125</t>
+          <t>530036</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381774</t>
+          <t>496233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>511541</t>
+          <t>566004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>271621</t>
+          <t>319968</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>248194</t>
+          <t>292914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290962</t>
+          <t>341434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>519087</t>
+          <t>453350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>475776</t>
+          <t>429143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>592724</t>
+          <t>476870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>790708</t>
+          <t>773317</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>741292</t>
+          <t>737349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871059</t>
+          <t>807120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>127589</t>
+          <t>127966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100146</t>
+          <t>102097</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153062</t>
+          <t>149875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>317768</t>
+          <t>357748</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>292492</t>
+          <t>330048</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343560</t>
+          <t>385291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>445357</t>
+          <t>485714</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>410970</t>
+          <t>450991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>483461</t>
+          <t>525419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>105623</t>
+          <t>97821</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80150</t>
+          <t>75912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133066</t>
+          <t>123690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>426142</t>
+          <t>460994</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>400350</t>
+          <t>433451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>451418</t>
+          <t>488694</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>531765</t>
+          <t>558815</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493661</t>
+          <t>519110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>566152</t>
+          <t>593538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1428348</t>
+          <t>1566015</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1067908</t>
+          <t>1501089</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1563159</t>
+          <t>1625189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1746034</t>
+          <t>1722267</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1602819</t>
+          <t>1669645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2114193</t>
+          <t>1775145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3174382</t>
+          <t>3288282</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2822385</t>
+          <t>3205123</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3496077</t>
+          <t>3372937</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1849234</t>
+          <t>1749809</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1714423</t>
+          <t>1690635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2209674</t>
+          <t>1814735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1754225</t>
+          <t>1810851</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1386066</t>
+          <t>1757973</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1897440</t>
+          <t>1863473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3603459</t>
+          <t>3560660</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3281764</t>
+          <t>3476005</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3955456</t>
+          <t>3643819</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3277582</t>
+          <t>3315824</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3277582</t>
+          <t>3315824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3277582</t>
+          <t>3315824</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6777841</t>
+          <t>6848942</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6777841</t>
+          <t>6848942</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6777841</t>
+          <t>6848942</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
